--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260610.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260610.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.82%</t>
+          <t>12.44%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.76%</t>
+          <t>10.43%</t>
         </is>
       </c>
     </row>
@@ -660,51 +660,51 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.94%</t>
+          <t>6.79%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>力成科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>22,138,000</t>
+          <t>1,764,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.26%</t>
+          <t>5.63%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>力成科技</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1,764,000</t>
+          <t>22,138,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.07%</t>
+          <t>5.18%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>4.29%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.62%</t>
         </is>
       </c>
     </row>
@@ -777,44 +777,44 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>聯詠科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>15,276,000</t>
+          <t>7,907,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>聯詠科技</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>7,907,000</t>
+          <t>15,276,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
@@ -858,68 +858,68 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>19,558,000</t>
+          <t>2,827,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.38%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2,827,000</t>
+          <t>14,334,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>14,334,000</t>
+          <t>19,558,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,44 +931,44 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>仁寶電腦</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>66,656,000</t>
+          <t>1,101,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台灣積體</t>
+          <t>仁寶電腦</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,101,000</t>
+          <t>66,656,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
@@ -990,29 +990,29 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>和碩聯合</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>14,856,000</t>
+          <t>23,608,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -1034,51 +1034,51 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>和碩聯合</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>23,608,000</t>
+          <t>19,861,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>19,861,000</t>
+          <t>14,856,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -1100,29 +1100,29 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>頎邦科技</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>6,921,000</t>
+          <t>1,807,102,346</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,678,954,055</t>
+          <t>7,631,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>頎邦科技</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>7,631,000</t>
+          <t>6,921,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1232,46 +1232,46 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>家登精密</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,697,000</t>
+          <t>14,453,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>家登精密</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,868,000</t>
+          <t>2,697,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,44 +1283,44 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,930,000</t>
+          <t>1,868,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>14,453,000</t>
+          <t>1,930,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
@@ -1342,51 +1342,51 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>908,072,462</t>
+          <t>29,406,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>29,406,000</t>
+          <t>866,152,462</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.02%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-294,553,581</t>
+          <t>-336,714,834</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.26%</t>
         </is>
       </c>
     </row>
